--- a/src/main/resources/excel/surver_detail_template.xlsx
+++ b/src/main/resources/excel/surver_detail_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\life\1\bootdo-main\src\main\resources\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD6B4677-731D-40D1-BA41-7ADC8525A4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8439F4C7-206B-47C3-A2F6-AA78D2014B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="169">
   <si>
     <t>设计申报项目形式审查一览表</t>
   </si>
@@ -179,6 +179,7 @@
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -190,6 +191,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -204,6 +206,7 @@
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -215,6 +218,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -229,31 +233,7 @@
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>环境、安全证明</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-（地方或上级政府主管部门盖章）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -265,6 +245,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -285,6 +266,7 @@
         <sz val="9"/>
         <color rgb="FF0070C0"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -296,6 +278,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -310,6 +293,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -321,6 +305,7 @@
         <sz val="9"/>
         <color rgb="FF0070C0"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -492,6 +477,7 @@
         <b/>
         <sz val="9"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -548,6 +534,7 @@
         <sz val="9"/>
         <color rgb="FFFF0000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -559,6 +546,7 @@
         <sz val="9"/>
         <color rgb="FF000000"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -583,138 +571,170 @@
     <t>新技术来源</t>
   </si>
   <si>
+    <t>水资源评价</t>
+  </si>
+  <si>
+    <t>上级主管部门评价</t>
+  </si>
+  <si>
+    <t>建设单位评价</t>
+  </si>
+  <si>
+    <t>标准设计申报项目形式审查一览表</t>
+  </si>
+  <si>
+    <t>主编单位</t>
+  </si>
+  <si>
+    <t>附件</t>
+  </si>
+  <si>
+    <t>图集名称</t>
+  </si>
+  <si>
+    <t>图集号</t>
+  </si>
+  <si>
+    <t>批准立项文件号</t>
+  </si>
+  <si>
+    <t>批准实施文件号</t>
+  </si>
+  <si>
+    <t>标准设计图集和文字说明总结</t>
+  </si>
+  <si>
+    <t>主管部门批准立项及出版的批文</t>
+  </si>
+  <si>
+    <t>两个以上用户使用证明</t>
+  </si>
+  <si>
+    <t>经济效益或使用效果证明</t>
+  </si>
+  <si>
+    <t>查新报告时间、报告出具单位</t>
+  </si>
+  <si>
+    <t>标准设计</t>
+  </si>
+  <si>
+    <t>注： 所有表格中分组栏不用填写。</t>
+  </si>
+  <si>
+    <t>软件申报项目形式审查一览表</t>
+  </si>
+  <si>
+    <t>软件全称</t>
+  </si>
+  <si>
+    <t>是否申报单位承担（本单位盖章）</t>
+  </si>
+  <si>
+    <t>申请表</t>
+  </si>
+  <si>
+    <t>软件简称</t>
+  </si>
+  <si>
+    <t>软件类型</t>
+  </si>
+  <si>
+    <t>软件类别</t>
+  </si>
+  <si>
+    <t>软件符合哪类现行国家过饭</t>
+  </si>
+  <si>
+    <t>开发起止时间</t>
+  </si>
+  <si>
+    <t>试用时间</t>
+  </si>
+  <si>
+    <t>使用说明书/用户手册</t>
+  </si>
+  <si>
+    <t>用户报告</t>
+  </si>
+  <si>
+    <t>推广应用时间范围数量证明</t>
+  </si>
+  <si>
+    <t>经济效益</t>
+  </si>
+  <si>
+    <t>软件</t>
+  </si>
+  <si>
+    <t>一等奖</t>
+  </si>
+  <si>
+    <t>最近三年无较大勘察设计质量安全事故承诺书</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>环境、安全及消防验收合格证明</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+（地方或上级政府主管部门盖章）</t>
+    </r>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试机构</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测评(鉴定或评价)时间</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测评(鉴定或评价)部门</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试时间</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>软件登记证书或行业测评(鉴定或评价)证书</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地下水开采经一年以上观测资料验证。提供盖章的一年以上的观测资料</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>规划、建设方验收报告</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>地下工程竣工后一年（建设单位出具证明）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>结构主体工程完成一年以上时间
-（建设单位出具）</t>
-  </si>
-  <si>
-    <t>地下工程竣工后一年</t>
-  </si>
-  <si>
-    <t>规划、建设方验收</t>
-  </si>
-  <si>
-    <t>地下水开采经一年以上观测资料验证</t>
-  </si>
-  <si>
-    <t>水资源评价</t>
-  </si>
-  <si>
-    <t>上级主管部门评价</t>
-  </si>
-  <si>
-    <t>建设单位评价</t>
-  </si>
-  <si>
-    <t>标准设计申报项目形式审查一览表</t>
-  </si>
-  <si>
-    <t>主编单位</t>
-  </si>
-  <si>
-    <t>附件</t>
-  </si>
-  <si>
-    <t>图集名称</t>
-  </si>
-  <si>
-    <t>图集号</t>
-  </si>
-  <si>
-    <t>批准立项文件号</t>
-  </si>
-  <si>
-    <t>批准实施文件号</t>
-  </si>
-  <si>
-    <t>标准设计图集和文字说明总结</t>
-  </si>
-  <si>
-    <t>主管部门批准立项及出版的批文</t>
-  </si>
-  <si>
-    <t>两个以上用户使用证明</t>
-  </si>
-  <si>
-    <t>经济效益或使用效果证明</t>
-  </si>
-  <si>
-    <t>查新报告时间、报告出具单位</t>
-  </si>
-  <si>
-    <t>标准设计</t>
-  </si>
-  <si>
-    <t>注： 所有表格中分组栏不用填写。</t>
-  </si>
-  <si>
-    <t>软件申报项目形式审查一览表</t>
-  </si>
-  <si>
-    <t>软件全称</t>
-  </si>
-  <si>
-    <t>是否申报单位承担（本单位盖章）</t>
-  </si>
-  <si>
-    <t>申请表</t>
-  </si>
-  <si>
-    <t>软件简称</t>
-  </si>
-  <si>
-    <t>软件类型</t>
-  </si>
-  <si>
-    <t>软件类别</t>
-  </si>
-  <si>
-    <t>软件符合哪类现行国家过饭</t>
-  </si>
-  <si>
-    <t>开发起止时间</t>
-  </si>
-  <si>
-    <t>试用时间</t>
-  </si>
-  <si>
-    <t>鉴定部门</t>
-  </si>
-  <si>
-    <t>鉴定时间</t>
-  </si>
-  <si>
-    <t>评测公司</t>
-  </si>
-  <si>
-    <t>评测时间</t>
-  </si>
-  <si>
-    <t>使用说明书/用户手册</t>
-  </si>
-  <si>
-    <t>软件登记证书或行业测评证书</t>
-  </si>
-  <si>
-    <t>用户报告</t>
-  </si>
-  <si>
-    <t>推广应用时间范围数量证明</t>
-  </si>
-  <si>
-    <t>经济效益</t>
-  </si>
-  <si>
-    <t>软件</t>
-  </si>
-  <si>
-    <t>一等奖</t>
+（建设单位出具证明）</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -726,6 +746,7 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -733,6 +754,7 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -740,6 +762,7 @@
       <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -747,6 +770,7 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -761,6 +785,7 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -769,36 +794,42 @@
       <sz val="9"/>
       <color rgb="FF0070C0"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -812,12 +843,14 @@
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -832,6 +865,7 @@
       <sz val="18"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -840,6 +874,7 @@
       <sz val="16"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="major"/>
     </font>
@@ -847,6 +882,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -854,6 +890,7 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -867,6 +904,7 @@
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -874,7 +912,17 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1025,7 +1073,7 @@
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1281,6 +1329,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1305,6 +1359,9 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1317,6 +1374,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1338,12 +1398,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -1365,9 +1428,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1377,10 +1437,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1803,444 +1863,444 @@
       <c r="BF1" s="84"/>
     </row>
     <row r="2" spans="1:68" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="90" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="88" t="s">
+      <c r="C2" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="88" t="s">
+      <c r="D2" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="88" t="s">
+      <c r="E2" s="90" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="88" t="s">
+      <c r="F2" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="88" t="s">
+      <c r="G2" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="88" t="s">
+      <c r="H2" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="90" t="s">
+      <c r="I2" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="88" t="s">
+      <c r="J2" s="90" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="88" t="s">
+      <c r="K2" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="88" t="s">
+      <c r="L2" s="90" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="91" t="s">
+      <c r="M2" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="91" t="s">
+      <c r="N2" s="93" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="92" t="s">
+      <c r="O2" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="91" t="s">
+      <c r="P2" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="Q2" s="91" t="s">
-        <v>17</v>
-      </c>
-      <c r="R2" s="85" t="s">
+      <c r="Q2" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="R2" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="85"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="85"/>
-      <c r="AE2" s="85"/>
-      <c r="AF2" s="85"/>
-      <c r="AG2" s="85" t="s">
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="87"/>
+      <c r="Z2" s="87"/>
+      <c r="AA2" s="87"/>
+      <c r="AB2" s="87"/>
+      <c r="AC2" s="87"/>
+      <c r="AD2" s="87"/>
+      <c r="AE2" s="87"/>
+      <c r="AF2" s="87"/>
+      <c r="AG2" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="AH2" s="85"/>
-      <c r="AI2" s="85"/>
-      <c r="AJ2" s="85"/>
-      <c r="AK2" s="85"/>
-      <c r="AL2" s="85"/>
-      <c r="AM2" s="85"/>
-      <c r="AN2" s="85"/>
-      <c r="AO2" s="85"/>
-      <c r="AP2" s="85"/>
-      <c r="AQ2" s="85" t="s">
+      <c r="AH2" s="87"/>
+      <c r="AI2" s="87"/>
+      <c r="AJ2" s="87"/>
+      <c r="AK2" s="87"/>
+      <c r="AL2" s="87"/>
+      <c r="AM2" s="87"/>
+      <c r="AN2" s="87"/>
+      <c r="AO2" s="87"/>
+      <c r="AP2" s="87"/>
+      <c r="AQ2" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AR2" s="85"/>
-      <c r="AS2" s="85"/>
-      <c r="AT2" s="85"/>
-      <c r="AU2" s="85"/>
-      <c r="AV2" s="85"/>
-      <c r="AW2" s="85"/>
-      <c r="AX2" s="85"/>
-      <c r="AY2" s="85"/>
-      <c r="AZ2" s="85"/>
-      <c r="BA2" s="85"/>
-      <c r="BB2" s="85"/>
-      <c r="BC2" s="85"/>
-      <c r="BD2" s="85"/>
-      <c r="BE2" s="85"/>
-      <c r="BF2" s="93" t="s">
+      <c r="AR2" s="87"/>
+      <c r="AS2" s="87"/>
+      <c r="AT2" s="87"/>
+      <c r="AU2" s="87"/>
+      <c r="AV2" s="87"/>
+      <c r="AW2" s="87"/>
+      <c r="AX2" s="87"/>
+      <c r="AY2" s="87"/>
+      <c r="AZ2" s="87"/>
+      <c r="BA2" s="87"/>
+      <c r="BB2" s="87"/>
+      <c r="BC2" s="87"/>
+      <c r="BD2" s="87"/>
+      <c r="BE2" s="87"/>
+      <c r="BF2" s="96" t="s">
         <v>21</v>
       </c>
-      <c r="BG2" s="91" t="s">
+      <c r="BG2" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="BH2" s="91" t="s">
+      <c r="BH2" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="BI2" s="91" t="s">
+      <c r="BI2" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="BJ2" s="91" t="s">
+      <c r="BJ2" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="BK2" s="91" t="s">
+      <c r="BK2" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="BL2" s="91" t="s">
+      <c r="BL2" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="BM2" s="91" t="s">
+      <c r="BM2" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="BN2" s="88" t="s">
+      <c r="BN2" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="BO2" s="88" t="s">
+      <c r="BO2" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="BP2" s="91" t="s">
+      <c r="BP2" s="93" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:68" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="88"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="92"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="93" t="s">
+      <c r="A3" s="90"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
+      <c r="L3" s="90"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="S3" s="93" t="s">
+      <c r="S3" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="93" t="s">
+      <c r="T3" s="96" t="s">
         <v>34</v>
       </c>
-      <c r="U3" s="93" t="s">
+      <c r="U3" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="V3" s="94" t="s">
+      <c r="V3" s="97" t="s">
         <v>36</v>
       </c>
-      <c r="W3" s="93" t="s">
+      <c r="W3" s="96" t="s">
         <v>37</v>
       </c>
-      <c r="X3" s="93" t="s">
+      <c r="X3" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="Y3" s="93" t="s">
+      <c r="Y3" s="96" t="s">
         <v>39</v>
       </c>
-      <c r="Z3" s="93" t="s">
+      <c r="Z3" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="AA3" s="93" t="s">
+      <c r="AA3" s="96" t="s">
         <v>41</v>
       </c>
-      <c r="AB3" s="85" t="s">
+      <c r="AB3" s="87" t="s">
         <v>42</v>
       </c>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85" t="s">
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="87"/>
+      <c r="AE3" s="87"/>
+      <c r="AF3" s="87"/>
+      <c r="AG3" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="85"/>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="85"/>
-      <c r="AO3" s="85"/>
-      <c r="AP3" s="94" t="s">
+      <c r="AH3" s="87"/>
+      <c r="AI3" s="87"/>
+      <c r="AJ3" s="87"/>
+      <c r="AK3" s="87"/>
+      <c r="AL3" s="87"/>
+      <c r="AM3" s="87"/>
+      <c r="AN3" s="87"/>
+      <c r="AO3" s="87"/>
+      <c r="AP3" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="AQ3" s="95" t="s">
+      <c r="AQ3" s="98" t="s">
         <v>45</v>
       </c>
-      <c r="AR3" s="95" t="s">
+      <c r="AR3" s="98" t="s">
         <v>46</v>
       </c>
-      <c r="AS3" s="95" t="s">
+      <c r="AS3" s="100" t="s">
+        <v>159</v>
+      </c>
+      <c r="AT3" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="AT3" s="95" t="s">
+      <c r="AU3" s="87" t="s">
         <v>48</v>
       </c>
-      <c r="AU3" s="85" t="s">
+      <c r="AV3" s="87"/>
+      <c r="AW3" s="87"/>
+      <c r="AX3" s="87"/>
+      <c r="AY3" s="98" t="s">
         <v>49</v>
       </c>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="85"/>
-      <c r="AY3" s="95" t="s">
+      <c r="AZ3" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="AZ3" s="94" t="s">
+      <c r="BA3" s="101" t="s">
         <v>51</v>
       </c>
-      <c r="BA3" s="97" t="s">
+      <c r="BB3" s="88" t="s">
         <v>52</v>
       </c>
-      <c r="BB3" s="86" t="s">
+      <c r="BC3" s="88"/>
+      <c r="BD3" s="88"/>
+      <c r="BE3" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="BC3" s="86"/>
-      <c r="BD3" s="86"/>
-      <c r="BE3" s="86" t="s">
-        <v>54</v>
-      </c>
-      <c r="BF3" s="99"/>
-      <c r="BG3" s="91"/>
-      <c r="BH3" s="91"/>
-      <c r="BI3" s="91"/>
-      <c r="BJ3" s="91"/>
-      <c r="BK3" s="91"/>
-      <c r="BL3" s="91"/>
-      <c r="BM3" s="91"/>
-      <c r="BN3" s="88"/>
-      <c r="BO3" s="88"/>
-      <c r="BP3" s="91"/>
+      <c r="BF3" s="103"/>
+      <c r="BG3" s="93"/>
+      <c r="BH3" s="93"/>
+      <c r="BI3" s="93"/>
+      <c r="BJ3" s="93"/>
+      <c r="BK3" s="93"/>
+      <c r="BL3" s="93"/>
+      <c r="BM3" s="93"/>
+      <c r="BN3" s="90"/>
+      <c r="BO3" s="90"/>
+      <c r="BP3" s="93"/>
     </row>
     <row r="4" spans="1:68" s="1" customFormat="1" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="88"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="88"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="88"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="88"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="88"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="88"/>
-      <c r="M4" s="91"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="91"/>
-      <c r="R4" s="93"/>
-      <c r="S4" s="93"/>
-      <c r="T4" s="93"/>
-      <c r="U4" s="93"/>
-      <c r="V4" s="94"/>
-      <c r="W4" s="93"/>
-      <c r="X4" s="93"/>
-      <c r="Y4" s="93"/>
-      <c r="Z4" s="93"/>
-      <c r="AA4" s="93"/>
-      <c r="AB4" s="95" t="s">
+      <c r="A4" s="90"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="92"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="93"/>
+      <c r="N4" s="93"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="93"/>
+      <c r="Q4" s="93"/>
+      <c r="R4" s="96"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="96"/>
+      <c r="U4" s="96"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="96"/>
+      <c r="X4" s="96"/>
+      <c r="Y4" s="96"/>
+      <c r="Z4" s="96"/>
+      <c r="AA4" s="96"/>
+      <c r="AB4" s="98" t="s">
+        <v>54</v>
+      </c>
+      <c r="AC4" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="AC4" s="95" t="s">
+      <c r="AD4" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="AD4" s="95" t="s">
+      <c r="AE4" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="AE4" s="95" t="s">
+      <c r="AF4" s="97" t="s">
         <v>58</v>
       </c>
-      <c r="AF4" s="94" t="s">
+      <c r="AG4" s="89" t="s">
         <v>59</v>
       </c>
-      <c r="AG4" s="87" t="s">
+      <c r="AH4" s="89"/>
+      <c r="AI4" s="89"/>
+      <c r="AJ4" s="89"/>
+      <c r="AK4" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="AH4" s="87"/>
-      <c r="AI4" s="87"/>
-      <c r="AJ4" s="87"/>
-      <c r="AK4" s="29" t="s">
+      <c r="AL4" s="88" t="s">
         <v>61</v>
       </c>
-      <c r="AL4" s="86" t="s">
+      <c r="AM4" s="88"/>
+      <c r="AN4" s="88"/>
+      <c r="AO4" s="88"/>
+      <c r="AP4" s="97"/>
+      <c r="AQ4" s="99"/>
+      <c r="AR4" s="99"/>
+      <c r="AS4" s="99"/>
+      <c r="AT4" s="99"/>
+      <c r="AU4" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="AM4" s="86"/>
-      <c r="AN4" s="86"/>
-      <c r="AO4" s="86"/>
-      <c r="AP4" s="94"/>
-      <c r="AQ4" s="96"/>
-      <c r="AR4" s="96"/>
-      <c r="AS4" s="96"/>
-      <c r="AT4" s="96"/>
-      <c r="AU4" s="85" t="s">
+      <c r="AV4" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="AV4" s="85" t="s">
+      <c r="AW4" s="87" t="s">
         <v>64</v>
       </c>
-      <c r="AW4" s="85" t="s">
+      <c r="AX4" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="AX4" s="85" t="s">
+      <c r="AY4" s="98"/>
+      <c r="AZ4" s="99"/>
+      <c r="BA4" s="102"/>
+      <c r="BB4" s="97" t="s">
         <v>66</v>
       </c>
-      <c r="AY4" s="95"/>
-      <c r="AZ4" s="96"/>
-      <c r="BA4" s="98"/>
-      <c r="BB4" s="94" t="s">
+      <c r="BC4" s="88" t="s">
         <v>67</v>
       </c>
-      <c r="BC4" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="BD4" s="86"/>
-      <c r="BE4" s="86"/>
-      <c r="BF4" s="99"/>
-      <c r="BG4" s="91"/>
-      <c r="BH4" s="91"/>
-      <c r="BI4" s="91"/>
-      <c r="BJ4" s="91"/>
-      <c r="BK4" s="91"/>
-      <c r="BL4" s="91"/>
-      <c r="BM4" s="91"/>
-      <c r="BN4" s="88"/>
-      <c r="BO4" s="88"/>
-      <c r="BP4" s="91"/>
+      <c r="BD4" s="88"/>
+      <c r="BE4" s="88"/>
+      <c r="BF4" s="103"/>
+      <c r="BG4" s="93"/>
+      <c r="BH4" s="93"/>
+      <c r="BI4" s="93"/>
+      <c r="BJ4" s="93"/>
+      <c r="BK4" s="93"/>
+      <c r="BL4" s="93"/>
+      <c r="BM4" s="93"/>
+      <c r="BN4" s="90"/>
+      <c r="BO4" s="90"/>
+      <c r="BP4" s="93"/>
     </row>
     <row r="5" spans="1:68" s="1" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="88"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="91"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="92"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="93"/>
-      <c r="S5" s="93"/>
-      <c r="T5" s="93"/>
-      <c r="U5" s="93"/>
-      <c r="V5" s="94"/>
-      <c r="W5" s="93"/>
-      <c r="X5" s="93"/>
-      <c r="Y5" s="93"/>
-      <c r="Z5" s="93"/>
-      <c r="AA5" s="93"/>
-      <c r="AB5" s="95"/>
-      <c r="AC5" s="95"/>
-      <c r="AD5" s="95"/>
-      <c r="AE5" s="95"/>
-      <c r="AF5" s="96"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="93"/>
+      <c r="N5" s="93"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="93"/>
+      <c r="Q5" s="93"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
+      <c r="T5" s="96"/>
+      <c r="U5" s="96"/>
+      <c r="V5" s="97"/>
+      <c r="W5" s="96"/>
+      <c r="X5" s="96"/>
+      <c r="Y5" s="96"/>
+      <c r="Z5" s="96"/>
+      <c r="AA5" s="96"/>
+      <c r="AB5" s="98"/>
+      <c r="AC5" s="98"/>
+      <c r="AD5" s="98"/>
+      <c r="AE5" s="98"/>
+      <c r="AF5" s="99"/>
       <c r="AG5" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH5" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="AH5" s="61" t="s">
+      <c r="AI5" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="AI5" s="61" t="s">
+      <c r="AJ5" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="AJ5" s="61" t="s">
+      <c r="AK5" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="AK5" s="61" t="s">
+      <c r="AL5" s="61" t="s">
+        <v>72</v>
+      </c>
+      <c r="AM5" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="AL5" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="AM5" s="61" t="s">
+      <c r="AN5" s="61" t="s">
         <v>74</v>
       </c>
-      <c r="AN5" s="61" t="s">
+      <c r="AO5" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="AO5" s="61" t="s">
+      <c r="AP5" s="97"/>
+      <c r="AQ5" s="99"/>
+      <c r="AR5" s="99"/>
+      <c r="AS5" s="99"/>
+      <c r="AT5" s="99"/>
+      <c r="AU5" s="87"/>
+      <c r="AV5" s="87"/>
+      <c r="AW5" s="87"/>
+      <c r="AX5" s="87"/>
+      <c r="AY5" s="98"/>
+      <c r="AZ5" s="99"/>
+      <c r="BA5" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="AP5" s="94"/>
-      <c r="AQ5" s="96"/>
-      <c r="AR5" s="96"/>
-      <c r="AS5" s="96"/>
-      <c r="AT5" s="96"/>
-      <c r="AU5" s="85"/>
-      <c r="AV5" s="85"/>
-      <c r="AW5" s="85"/>
-      <c r="AX5" s="85"/>
-      <c r="AY5" s="95"/>
-      <c r="AZ5" s="96"/>
-      <c r="BA5" s="29" t="s">
+      <c r="BB5" s="97"/>
+      <c r="BC5" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="BB5" s="94"/>
-      <c r="BC5" s="61" t="s">
+      <c r="BD5" s="61" t="s">
         <v>78</v>
       </c>
-      <c r="BD5" s="61" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE5" s="86"/>
-      <c r="BF5" s="99"/>
-      <c r="BG5" s="91"/>
-      <c r="BH5" s="91"/>
-      <c r="BI5" s="91"/>
-      <c r="BJ5" s="91"/>
-      <c r="BK5" s="91"/>
-      <c r="BL5" s="91"/>
-      <c r="BM5" s="91"/>
-      <c r="BN5" s="88"/>
-      <c r="BO5" s="88"/>
-      <c r="BP5" s="91"/>
+      <c r="BE5" s="88"/>
+      <c r="BF5" s="103"/>
+      <c r="BG5" s="93"/>
+      <c r="BH5" s="93"/>
+      <c r="BI5" s="93"/>
+      <c r="BJ5" s="93"/>
+      <c r="BK5" s="93"/>
+      <c r="BL5" s="93"/>
+      <c r="BM5" s="93"/>
+      <c r="BN5" s="90"/>
+      <c r="BO5" s="90"/>
+      <c r="BP5" s="93"/>
     </row>
     <row r="6" spans="1:68" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
@@ -2249,7 +2309,7 @@
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E6" s="10">
         <v>1.01</v>
@@ -2260,136 +2320,136 @@
       <c r="I6" s="38"/>
       <c r="J6" s="47"/>
       <c r="K6" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="L6" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="L6" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="M6" s="12">
         <v>1</v>
       </c>
       <c r="N6" s="47" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O6" s="24"/>
       <c r="P6" s="47"/>
       <c r="Q6" s="31"/>
       <c r="R6" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="S6" s="68" t="s">
         <v>84</v>
       </c>
-      <c r="S6" s="68" t="s">
+      <c r="T6" s="68" t="s">
         <v>85</v>
-      </c>
-      <c r="T6" s="68" t="s">
-        <v>86</v>
       </c>
       <c r="U6" s="68"/>
       <c r="V6" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="W6" s="80" t="s">
         <v>87</v>
       </c>
-      <c r="W6" s="80" t="s">
+      <c r="X6" s="80" t="s">
         <v>88</v>
       </c>
-      <c r="X6" s="80" t="s">
+      <c r="Y6" s="80" t="s">
         <v>89</v>
       </c>
-      <c r="Y6" s="80" t="s">
-        <v>90</v>
-      </c>
       <c r="Z6" s="80" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AA6" s="80"/>
       <c r="AB6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AC6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AD6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AE6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AF6" s="81" t="s">
         <v>91</v>
       </c>
-      <c r="AC6" s="27" t="s">
+      <c r="AG6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AI6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AJ6" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK6" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="AD6" s="27" t="s">
+      <c r="AL6" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="AE6" s="27" t="s">
+      <c r="AM6" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="AF6" s="81" t="s">
+      <c r="AN6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO6" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AP6" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ6" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="AG6" s="27" t="s">
+      <c r="AR6" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AS6" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AT6" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AU6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AV6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AW6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AY6" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="AZ6" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="BA6" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="AH6" s="27" t="s">
+      <c r="BB6" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="AI6" s="27" t="s">
+      <c r="BC6" s="58" t="s">
         <v>91</v>
       </c>
-      <c r="AJ6" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AL6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AM6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AN6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AO6" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="AP6" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ6" s="28" t="s">
-        <v>93</v>
-      </c>
-      <c r="AR6" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS6" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AT6" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="AU6" s="27" t="s">
+      <c r="BD6" s="58" t="s">
         <v>91</v>
-      </c>
-      <c r="AV6" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AW6" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AX6" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AY6" s="27" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ6" s="28" t="s">
-        <v>96</v>
-      </c>
-      <c r="BA6" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="BB6" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="BC6" s="58" t="s">
-        <v>92</v>
-      </c>
-      <c r="BD6" s="58" t="s">
-        <v>92</v>
       </c>
       <c r="BE6" s="28"/>
       <c r="BF6" s="67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="BG6" s="45"/>
       <c r="BH6" s="45"/>
@@ -2416,10 +2476,10 @@
       <c r="I7" s="38"/>
       <c r="J7" s="47"/>
       <c r="K7" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="L7" s="38" t="s">
         <v>81</v>
-      </c>
-      <c r="L7" s="38" t="s">
-        <v>82</v>
       </c>
       <c r="M7" s="12">
         <v>2</v>
@@ -2457,7 +2517,7 @@
       <c r="AR7" s="28"/>
       <c r="AS7" s="28"/>
       <c r="AT7" s="28" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AU7" s="28"/>
       <c r="AV7" s="28"/>
@@ -2484,7 +2544,7 @@
     </row>
     <row r="8" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L8" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2493,12 +2553,12 @@
     <row r="12" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" spans="1:68" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="77" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2506,41 +2566,41 @@
     <sortCondition ref="M6"/>
   </sortState>
   <mergeCells count="67">
-    <mergeCell ref="BL2:BL5"/>
     <mergeCell ref="BM2:BM5"/>
     <mergeCell ref="BN2:BN5"/>
     <mergeCell ref="BO2:BO5"/>
     <mergeCell ref="BP2:BP5"/>
-    <mergeCell ref="BG2:BG5"/>
     <mergeCell ref="BH2:BH5"/>
     <mergeCell ref="BI2:BI5"/>
     <mergeCell ref="BJ2:BJ5"/>
     <mergeCell ref="BK2:BK5"/>
-    <mergeCell ref="AZ3:AZ5"/>
+    <mergeCell ref="BL2:BL5"/>
     <mergeCell ref="BA3:BA4"/>
     <mergeCell ref="BB4:BB5"/>
     <mergeCell ref="BE3:BE5"/>
     <mergeCell ref="BF2:BF5"/>
-    <mergeCell ref="AU4:AU5"/>
-    <mergeCell ref="AV4:AV5"/>
-    <mergeCell ref="AW4:AW5"/>
-    <mergeCell ref="AX4:AX5"/>
-    <mergeCell ref="AY3:AY5"/>
-    <mergeCell ref="AP3:AP5"/>
-    <mergeCell ref="AQ3:AQ5"/>
-    <mergeCell ref="AR3:AR5"/>
-    <mergeCell ref="AS3:AS5"/>
-    <mergeCell ref="AT3:AT5"/>
-    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="BG2:BG5"/>
     <mergeCell ref="AC4:AC5"/>
     <mergeCell ref="AD4:AD5"/>
     <mergeCell ref="AE4:AE5"/>
     <mergeCell ref="AF4:AF5"/>
+    <mergeCell ref="AP3:AP5"/>
     <mergeCell ref="N2:N5"/>
     <mergeCell ref="O2:O5"/>
     <mergeCell ref="P2:P5"/>
     <mergeCell ref="Q2:Q5"/>
     <mergeCell ref="R3:R5"/>
+    <mergeCell ref="R2:AF2"/>
+    <mergeCell ref="S3:S5"/>
+    <mergeCell ref="T3:T5"/>
+    <mergeCell ref="U3:U5"/>
+    <mergeCell ref="V3:V5"/>
+    <mergeCell ref="W3:W5"/>
+    <mergeCell ref="X3:X5"/>
+    <mergeCell ref="Y3:Y5"/>
+    <mergeCell ref="Z3:Z5"/>
+    <mergeCell ref="AA3:AA5"/>
+    <mergeCell ref="AB4:AB5"/>
     <mergeCell ref="AG4:AJ4"/>
     <mergeCell ref="AL4:AO4"/>
     <mergeCell ref="BC4:BD4"/>
@@ -2557,26 +2617,26 @@
     <mergeCell ref="K2:K5"/>
     <mergeCell ref="L2:L5"/>
     <mergeCell ref="M2:M5"/>
-    <mergeCell ref="R2:AF2"/>
     <mergeCell ref="AG2:AP2"/>
     <mergeCell ref="AQ2:BE2"/>
     <mergeCell ref="AB3:AF3"/>
     <mergeCell ref="AG3:AO3"/>
     <mergeCell ref="AU3:AX3"/>
     <mergeCell ref="BB3:BD3"/>
-    <mergeCell ref="S3:S5"/>
-    <mergeCell ref="T3:T5"/>
-    <mergeCell ref="U3:U5"/>
-    <mergeCell ref="V3:V5"/>
-    <mergeCell ref="W3:W5"/>
-    <mergeCell ref="X3:X5"/>
-    <mergeCell ref="Y3:Y5"/>
-    <mergeCell ref="Z3:Z5"/>
-    <mergeCell ref="AA3:AA5"/>
+    <mergeCell ref="AQ3:AQ5"/>
+    <mergeCell ref="AR3:AR5"/>
+    <mergeCell ref="AS3:AS5"/>
+    <mergeCell ref="AT3:AT5"/>
+    <mergeCell ref="AU4:AU5"/>
+    <mergeCell ref="AV4:AV5"/>
+    <mergeCell ref="AW4:AW5"/>
+    <mergeCell ref="AX4:AX5"/>
+    <mergeCell ref="AY3:AY5"/>
+    <mergeCell ref="AZ3:AZ5"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="8" firstPageNumber="4294963191" orientation="landscape" useFirstPageNumber="1"/>
+  <pageSetup paperSize="8" firstPageNumber="4294963191" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
     <oddFooter>&amp;C&amp;P</oddFooter>
   </headerFooter>
@@ -2601,7 +2661,9 @@
     <col min="26" max="29" width="5.5546875" style="50" customWidth="1"/>
     <col min="30" max="30" width="8.21875" style="50" customWidth="1"/>
     <col min="31" max="33" width="6.44140625" style="50" customWidth="1"/>
-    <col min="34" max="37" width="8.21875" style="50" customWidth="1"/>
+    <col min="34" max="35" width="8.21875" style="50" customWidth="1"/>
+    <col min="36" max="36" width="7.77734375" style="50" customWidth="1"/>
+    <col min="37" max="37" width="10.88671875" style="50" customWidth="1"/>
     <col min="38" max="44" width="5.88671875" style="50" customWidth="1"/>
     <col min="45" max="45" width="7.6640625" style="49" customWidth="1"/>
     <col min="46" max="46" width="5.88671875" style="50" customWidth="1"/>
@@ -2616,7 +2678,7 @@
   <sheetData>
     <row r="1" spans="1:57" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K1" s="55"/>
       <c r="N1" s="56"/>
@@ -2654,317 +2716,317 @@
       <c r="AU1" s="66"/>
     </row>
     <row r="2" spans="1:57" s="48" customFormat="1" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="106" t="s">
+      <c r="B2" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="104" t="s">
+      <c r="C2" s="110" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="104" t="s">
+      <c r="D2" s="110" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="104" t="s">
+      <c r="E2" s="110" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="104" t="s">
+      <c r="F2" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="93" t="s">
+      <c r="G2" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="93" t="s">
+      <c r="H2" s="96" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="113" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="114" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="114" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="110" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="116" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="116" t="s">
         <v>103</v>
       </c>
-      <c r="I2" s="108" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="93" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="104" t="s">
-        <v>11</v>
-      </c>
-      <c r="L2" s="93" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="109" t="s">
-        <v>13</v>
-      </c>
-      <c r="N2" s="109" t="s">
-        <v>14</v>
-      </c>
-      <c r="O2" s="104" t="s">
-        <v>15</v>
-      </c>
-      <c r="P2" s="111" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q2" s="111" t="s">
+      <c r="R2" s="87" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="87"/>
+      <c r="Z2" s="87"/>
+      <c r="AA2" s="87"/>
+      <c r="AB2" s="87"/>
+      <c r="AC2" s="87"/>
+      <c r="AD2" s="102" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE2" s="102"/>
+      <c r="AF2" s="102"/>
+      <c r="AG2" s="102"/>
+      <c r="AH2" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI2" s="104"/>
+      <c r="AJ2" s="104"/>
+      <c r="AK2" s="104"/>
+      <c r="AL2" s="105"/>
+      <c r="AM2" s="105"/>
+      <c r="AN2" s="105"/>
+      <c r="AO2" s="105"/>
+      <c r="AP2" s="105"/>
+      <c r="AQ2" s="105"/>
+      <c r="AR2" s="105"/>
+      <c r="AS2" s="106"/>
+      <c r="AT2" s="107"/>
+      <c r="AU2" s="110" t="s">
         <v>104</v>
       </c>
-      <c r="R2" s="85" t="s">
-        <v>18</v>
-      </c>
-      <c r="S2" s="85"/>
-      <c r="T2" s="85"/>
-      <c r="U2" s="85"/>
-      <c r="V2" s="85"/>
-      <c r="W2" s="85"/>
-      <c r="X2" s="85"/>
-      <c r="Y2" s="85"/>
-      <c r="Z2" s="85"/>
-      <c r="AA2" s="85"/>
-      <c r="AB2" s="85"/>
-      <c r="AC2" s="85"/>
-      <c r="AD2" s="98" t="s">
-        <v>19</v>
-      </c>
-      <c r="AE2" s="98"/>
-      <c r="AF2" s="98"/>
-      <c r="AG2" s="98"/>
-      <c r="AH2" s="100" t="s">
-        <v>20</v>
-      </c>
-      <c r="AI2" s="100"/>
-      <c r="AJ2" s="100"/>
-      <c r="AK2" s="100"/>
-      <c r="AL2" s="101"/>
-      <c r="AM2" s="101"/>
-      <c r="AN2" s="101"/>
-      <c r="AO2" s="101"/>
-      <c r="AP2" s="101"/>
-      <c r="AQ2" s="101"/>
-      <c r="AR2" s="101"/>
-      <c r="AS2" s="102"/>
-      <c r="AT2" s="103"/>
-      <c r="AU2" s="104" t="s">
-        <v>105</v>
-      </c>
-      <c r="AV2" s="91" t="s">
+      <c r="AV2" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="AW2" s="91" t="s">
+      <c r="AW2" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="AX2" s="91" t="s">
+      <c r="AX2" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="AY2" s="91" t="s">
+      <c r="AY2" s="93" t="s">
         <v>25</v>
       </c>
-      <c r="AZ2" s="91" t="s">
+      <c r="AZ2" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="BA2" s="91" t="s">
+      <c r="BA2" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="BB2" s="91" t="s">
+      <c r="BB2" s="93" t="s">
         <v>28</v>
       </c>
-      <c r="BC2" s="114" t="s">
+      <c r="BC2" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="BD2" s="114" t="s">
+      <c r="BD2" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="BE2" s="91" t="s">
+      <c r="BE2" s="93" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:57" s="48" customFormat="1" ht="52.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="105"/>
-      <c r="B3" s="107"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="105"/>
-      <c r="E3" s="105"/>
-      <c r="F3" s="105"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="108"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="93"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="105" t="s">
+      <c r="A3" s="108"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="108"/>
+      <c r="D3" s="108"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="113"/>
+      <c r="J3" s="96"/>
+      <c r="K3" s="108"/>
+      <c r="L3" s="96"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="108"/>
+      <c r="P3" s="117"/>
+      <c r="Q3" s="117"/>
+      <c r="R3" s="108" t="s">
+        <v>105</v>
+      </c>
+      <c r="S3" s="108" t="s">
         <v>106</v>
       </c>
-      <c r="S3" s="105" t="s">
+      <c r="T3" s="108" t="s">
+        <v>34</v>
+      </c>
+      <c r="U3" s="108" t="s">
+        <v>35</v>
+      </c>
+      <c r="V3" s="108" t="s">
         <v>107</v>
       </c>
-      <c r="T3" s="105" t="s">
-        <v>34</v>
-      </c>
-      <c r="U3" s="105" t="s">
-        <v>35</v>
-      </c>
-      <c r="V3" s="105" t="s">
+      <c r="W3" s="108" t="s">
         <v>108</v>
       </c>
-      <c r="W3" s="105" t="s">
+      <c r="X3" s="108" t="s">
         <v>109</v>
       </c>
-      <c r="X3" s="105" t="s">
+      <c r="Y3" s="108" t="s">
         <v>110</v>
       </c>
-      <c r="Y3" s="105" t="s">
+      <c r="Z3" s="87" t="s">
         <v>111</v>
       </c>
-      <c r="Z3" s="85" t="s">
+      <c r="AA3" s="87"/>
+      <c r="AB3" s="87"/>
+      <c r="AC3" s="87"/>
+      <c r="AD3" s="98" t="s">
         <v>112</v>
       </c>
-      <c r="AA3" s="85"/>
-      <c r="AB3" s="85"/>
-      <c r="AC3" s="85"/>
-      <c r="AD3" s="95" t="s">
+      <c r="AE3" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="AE3" s="95" t="s">
+      <c r="AF3" s="97" t="s">
         <v>114</v>
       </c>
-      <c r="AF3" s="94" t="s">
+      <c r="AG3" s="97" t="s">
+        <v>44</v>
+      </c>
+      <c r="AH3" s="26" t="s">
         <v>115</v>
       </c>
-      <c r="AG3" s="94" t="s">
-        <v>44</v>
-      </c>
-      <c r="AH3" s="26" t="s">
+      <c r="AI3" s="26" t="s">
         <v>116</v>
       </c>
-      <c r="AI3" s="26" t="s">
+      <c r="AJ3" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="AJ3" s="26" t="s">
+      <c r="AK3" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="AK3" s="26" t="s">
+      <c r="AL3" s="98" t="s">
         <v>119</v>
       </c>
-      <c r="AL3" s="95" t="s">
+      <c r="AM3" s="98" t="s">
         <v>120</v>
       </c>
-      <c r="AM3" s="95" t="s">
+      <c r="AN3" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="AN3" s="29" t="s">
+      <c r="AO3" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="AO3" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="AP3" s="86" t="s">
+      <c r="AP3" s="88" t="s">
+        <v>52</v>
+      </c>
+      <c r="AQ3" s="88"/>
+      <c r="AR3" s="88"/>
+      <c r="AS3" s="111" t="s">
+        <v>50</v>
+      </c>
+      <c r="AT3" s="88" t="s">
         <v>53</v>
       </c>
-      <c r="AQ3" s="86"/>
-      <c r="AR3" s="86"/>
-      <c r="AS3" s="106" t="s">
-        <v>51</v>
-      </c>
-      <c r="AT3" s="86" t="s">
-        <v>54</v>
-      </c>
-      <c r="AU3" s="105"/>
-      <c r="AV3" s="91"/>
-      <c r="AW3" s="91"/>
-      <c r="AX3" s="91"/>
-      <c r="AY3" s="91"/>
-      <c r="AZ3" s="91"/>
-      <c r="BA3" s="91"/>
-      <c r="BB3" s="91"/>
-      <c r="BC3" s="115"/>
-      <c r="BD3" s="115"/>
-      <c r="BE3" s="91"/>
+      <c r="AU3" s="108"/>
+      <c r="AV3" s="93"/>
+      <c r="AW3" s="93"/>
+      <c r="AX3" s="93"/>
+      <c r="AY3" s="93"/>
+      <c r="AZ3" s="93"/>
+      <c r="BA3" s="93"/>
+      <c r="BB3" s="93"/>
+      <c r="BC3" s="119"/>
+      <c r="BD3" s="119"/>
+      <c r="BE3" s="93"/>
     </row>
     <row r="4" spans="1:57" s="48" customFormat="1" ht="94.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="105"/>
-      <c r="B4" s="107"/>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113"/>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="108"/>
+      <c r="D4" s="108"/>
+      <c r="E4" s="108"/>
+      <c r="F4" s="108"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="96"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="96"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="109"/>
+      <c r="S4" s="109"/>
+      <c r="T4" s="109"/>
+      <c r="U4" s="109"/>
+      <c r="V4" s="109"/>
+      <c r="W4" s="109"/>
+      <c r="X4" s="109"/>
+      <c r="Y4" s="109"/>
       <c r="Z4" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA4" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="AA4" s="62" t="s">
-        <v>56</v>
-      </c>
       <c r="AB4" s="62" t="s">
+        <v>123</v>
+      </c>
+      <c r="AC4" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="AC4" s="9" t="s">
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="97"/>
+      <c r="AG4" s="97"/>
+      <c r="AH4" s="60" t="s">
+        <v>168</v>
+      </c>
+      <c r="AI4" s="60" t="s">
+        <v>167</v>
+      </c>
+      <c r="AJ4" s="60" t="s">
+        <v>166</v>
+      </c>
+      <c r="AK4" s="60" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL4" s="99"/>
+      <c r="AM4" s="99"/>
+      <c r="AN4" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO4" s="29" t="s">
         <v>125</v>
       </c>
-      <c r="AD4" s="95"/>
-      <c r="AE4" s="95"/>
-      <c r="AF4" s="94"/>
-      <c r="AG4" s="94"/>
-      <c r="AH4" s="60" t="s">
+      <c r="AP4" s="61" t="s">
+        <v>66</v>
+      </c>
+      <c r="AQ4" s="61" t="s">
         <v>126</v>
       </c>
-      <c r="AI4" s="60" t="s">
+      <c r="AR4" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="AJ4" s="60" t="s">
-        <v>128</v>
-      </c>
-      <c r="AK4" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="AL4" s="96"/>
-      <c r="AM4" s="96"/>
-      <c r="AN4" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="AO4" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP4" s="61" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ4" s="61" t="s">
-        <v>131</v>
-      </c>
-      <c r="AR4" s="61" t="s">
-        <v>132</v>
-      </c>
-      <c r="AS4" s="107"/>
-      <c r="AT4" s="86"/>
-      <c r="AU4" s="105"/>
-      <c r="AV4" s="91"/>
-      <c r="AW4" s="91"/>
-      <c r="AX4" s="91"/>
-      <c r="AY4" s="91"/>
-      <c r="AZ4" s="91"/>
-      <c r="BA4" s="91"/>
-      <c r="BB4" s="91"/>
-      <c r="BC4" s="116"/>
-      <c r="BD4" s="116"/>
-      <c r="BE4" s="91"/>
+      <c r="AS4" s="112"/>
+      <c r="AT4" s="88"/>
+      <c r="AU4" s="108"/>
+      <c r="AV4" s="93"/>
+      <c r="AW4" s="93"/>
+      <c r="AX4" s="93"/>
+      <c r="AY4" s="93"/>
+      <c r="AZ4" s="93"/>
+      <c r="BA4" s="93"/>
+      <c r="BB4" s="93"/>
+      <c r="BC4" s="120"/>
+      <c r="BD4" s="120"/>
+      <c r="BE4" s="93"/>
     </row>
     <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="J5" s="50"/>
@@ -3031,7 +3093,6 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="BC2:BC4"/>
     <mergeCell ref="BD2:BD4"/>
     <mergeCell ref="BE2:BE4"/>
     <mergeCell ref="AX2:AX4"/>
@@ -3039,16 +3100,17 @@
     <mergeCell ref="AZ2:AZ4"/>
     <mergeCell ref="BA2:BA4"/>
     <mergeCell ref="BB2:BB4"/>
-    <mergeCell ref="AS3:AS4"/>
     <mergeCell ref="AT3:AT4"/>
     <mergeCell ref="AU2:AU4"/>
     <mergeCell ref="AV2:AV4"/>
     <mergeCell ref="AW2:AW4"/>
+    <mergeCell ref="BC2:BC4"/>
     <mergeCell ref="P2:P4"/>
     <mergeCell ref="Q2:Q4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="R2:AC2"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="L2:L4"/>
     <mergeCell ref="M2:M4"/>
@@ -3064,7 +3126,6 @@
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
-    <mergeCell ref="R2:AC2"/>
     <mergeCell ref="AD2:AG2"/>
     <mergeCell ref="AH2:AT2"/>
     <mergeCell ref="Z3:AC3"/>
@@ -3080,6 +3141,7 @@
     <mergeCell ref="AG3:AG4"/>
     <mergeCell ref="AL3:AL4"/>
     <mergeCell ref="AM3:AM4"/>
+    <mergeCell ref="AS3:AS4"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -3113,7 +3175,7 @@
   <sheetData>
     <row r="1" spans="1:39" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B1" s="6"/>
       <c r="H1" s="16"/>
@@ -3161,168 +3223,168 @@
       <c r="AC2" s="16"/>
     </row>
     <row r="3" spans="1:39" s="1" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="D3" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="93" t="s">
+      <c r="F3" s="96" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="93" t="s">
+      <c r="G3" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" s="108" t="s">
+      <c r="H3" s="96" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="104" t="s">
+      <c r="J3" s="110" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="93" t="s">
+      <c r="K3" s="96" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="104" t="s">
+      <c r="L3" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="109" t="s">
+      <c r="M3" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="95" t="s">
+      <c r="N3" s="98" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="104" t="s">
+      <c r="O3" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="95" t="s">
+      <c r="P3" s="98" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="109" t="s">
+      <c r="Q3" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="98" t="s">
+      <c r="R3" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
-      <c r="W3" s="98" t="s">
-        <v>135</v>
-      </c>
-      <c r="X3" s="98"/>
-      <c r="Y3" s="98"/>
-      <c r="Z3" s="98"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="104" t="s">
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="AD3" s="95" t="s">
+      <c r="AD3" s="98" t="s">
         <v>22</v>
       </c>
-      <c r="AE3" s="95" t="s">
+      <c r="AE3" s="98" t="s">
         <v>23</v>
       </c>
-      <c r="AF3" s="95" t="s">
+      <c r="AF3" s="98" t="s">
         <v>24</v>
       </c>
-      <c r="AG3" s="95" t="s">
+      <c r="AG3" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="AH3" s="95" t="s">
+      <c r="AH3" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="AI3" s="95" t="s">
+      <c r="AI3" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="AJ3" s="95" t="s">
+      <c r="AJ3" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="AK3" s="93" t="s">
+      <c r="AK3" s="96" t="s">
         <v>29</v>
       </c>
-      <c r="AL3" s="93" t="s">
+      <c r="AL3" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="AM3" s="95" t="s">
+      <c r="AM3" s="98" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:39" s="1" customFormat="1" ht="58.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="93"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="113"/>
-      <c r="K4" s="93"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="118"/>
+      <c r="A4" s="96"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="96"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="121"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="109"/>
+      <c r="P4" s="98"/>
+      <c r="Q4" s="121"/>
       <c r="R4" s="41" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="S4" s="41" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="T4" s="41" t="s">
         <v>32</v>
       </c>
       <c r="U4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="W4" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="X4" s="26" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y4" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="Z4" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="AA4" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="AB4" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="W4" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="X4" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y4" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="Z4" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA4" s="26" t="s">
-        <v>121</v>
-      </c>
-      <c r="AB4" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="AC4" s="105"/>
-      <c r="AD4" s="95"/>
-      <c r="AE4" s="95"/>
-      <c r="AF4" s="95"/>
-      <c r="AG4" s="95"/>
-      <c r="AH4" s="95"/>
-      <c r="AI4" s="95"/>
-      <c r="AJ4" s="95"/>
-      <c r="AK4" s="93"/>
-      <c r="AL4" s="93"/>
-      <c r="AM4" s="95"/>
+      <c r="AC4" s="108"/>
+      <c r="AD4" s="98"/>
+      <c r="AE4" s="98"/>
+      <c r="AF4" s="98"/>
+      <c r="AG4" s="98"/>
+      <c r="AH4" s="98"/>
+      <c r="AI4" s="98"/>
+      <c r="AJ4" s="98"/>
+      <c r="AK4" s="96"/>
+      <c r="AL4" s="96"/>
+      <c r="AM4" s="98"/>
     </row>
     <row r="5" spans="1:39" s="35" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
@@ -3335,7 +3397,7 @@
       <c r="H5" s="38"/>
       <c r="I5" s="18"/>
       <c r="J5" s="18" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="K5" s="38"/>
       <c r="L5" s="12"/>
@@ -3453,7 +3515,7 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="L8" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3"/>
@@ -3482,7 +3544,7 @@
     </row>
     <row r="12" spans="1:39" ht="48" x14ac:dyDescent="0.25">
       <c r="F12" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G12" s="14"/>
       <c r="H12" s="14"/>
@@ -3513,15 +3575,15 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -3547,7 +3609,9 @@
     <col min="17" max="17" width="12.21875" style="3" customWidth="1"/>
     <col min="18" max="24" width="9" style="3"/>
     <col min="25" max="26" width="11.33203125" style="3" customWidth="1"/>
-    <col min="27" max="32" width="9" style="3"/>
+    <col min="27" max="29" width="9" style="3"/>
+    <col min="30" max="30" width="10" style="3" customWidth="1"/>
+    <col min="31" max="32" width="9" style="3"/>
     <col min="33" max="33" width="5.6640625" style="3" customWidth="1"/>
     <col min="34" max="36" width="9" style="3"/>
     <col min="37" max="37" width="22.6640625" style="3" customWidth="1"/>
@@ -3556,7 +3620,7 @@
   <sheetData>
     <row r="1" spans="1:45" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="B1" s="6"/>
       <c r="J1" s="15"/>
@@ -3628,192 +3692,192 @@
       <c r="AS2" s="7"/>
     </row>
     <row r="3" spans="1:45" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="93" t="s">
+      <c r="C3" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="93" t="s">
+      <c r="D3" s="96" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="93" t="s">
+      <c r="E3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="93" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="93" t="s">
+      <c r="F3" s="96" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="93" t="s">
-        <v>134</v>
-      </c>
-      <c r="I3" s="108" t="s">
+      <c r="H3" s="96" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="113" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="93" t="s">
+      <c r="J3" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="104" t="s">
+      <c r="K3" s="110" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="104" t="s">
+      <c r="L3" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="109" t="s">
+      <c r="M3" s="114" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="109" t="s">
-        <v>149</v>
-      </c>
-      <c r="O3" s="104" t="s">
+      <c r="N3" s="114" t="s">
+        <v>144</v>
+      </c>
+      <c r="O3" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="109" t="s">
+      <c r="P3" s="114" t="s">
         <v>16</v>
       </c>
-      <c r="Q3" s="109" t="s">
+      <c r="Q3" s="114" t="s">
         <v>17</v>
       </c>
-      <c r="R3" s="98" t="s">
-        <v>150</v>
-      </c>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
-      <c r="W3" s="98"/>
-      <c r="X3" s="98"/>
-      <c r="Y3" s="98"/>
-      <c r="Z3" s="98"/>
-      <c r="AA3" s="98"/>
+      <c r="R3" s="102" t="s">
+        <v>145</v>
+      </c>
+      <c r="S3" s="102"/>
+      <c r="T3" s="102"/>
+      <c r="U3" s="102"/>
+      <c r="V3" s="102"/>
+      <c r="W3" s="102"/>
+      <c r="X3" s="102"/>
+      <c r="Y3" s="102"/>
+      <c r="Z3" s="102"/>
+      <c r="AA3" s="102"/>
       <c r="AB3" s="22"/>
-      <c r="AC3" s="98" t="s">
+      <c r="AC3" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="98"/>
-      <c r="AE3" s="98"/>
-      <c r="AF3" s="98"/>
-      <c r="AG3" s="98"/>
-      <c r="AH3" s="98"/>
-      <c r="AI3" s="119" t="s">
+      <c r="AD3" s="102"/>
+      <c r="AE3" s="102"/>
+      <c r="AF3" s="102"/>
+      <c r="AG3" s="102"/>
+      <c r="AH3" s="102"/>
+      <c r="AI3" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="AJ3" s="111" t="s">
+      <c r="AJ3" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="AK3" s="111" t="s">
+      <c r="AK3" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="AL3" s="111" t="s">
+      <c r="AL3" s="116" t="s">
         <v>24</v>
       </c>
-      <c r="AM3" s="111" t="s">
+      <c r="AM3" s="116" t="s">
         <v>25</v>
       </c>
-      <c r="AN3" s="111" t="s">
+      <c r="AN3" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="AO3" s="111" t="s">
+      <c r="AO3" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="AP3" s="111" t="s">
+      <c r="AP3" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="AQ3" s="114" t="s">
+      <c r="AQ3" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="AR3" s="114" t="s">
+      <c r="AR3" s="118" t="s">
         <v>30</v>
       </c>
-      <c r="AS3" s="111" t="s">
+      <c r="AS3" s="116" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:45" s="1" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="104"/>
-      <c r="B4" s="117"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="108"/>
-      <c r="J4" s="104"/>
-      <c r="K4" s="113"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="105"/>
-      <c r="P4" s="110"/>
-      <c r="Q4" s="110"/>
+      <c r="A4" s="110"/>
+      <c r="B4" s="122"/>
+      <c r="C4" s="96"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="96"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="113"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="109"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="108"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
       <c r="R4" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="S4" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="T4" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="U4" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="V4" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="W4" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="X4" s="23" t="s">
         <v>151</v>
       </c>
-      <c r="S4" s="23" t="s">
+      <c r="Y4" s="85" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z4" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="AA4" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB4" s="85" t="s">
+        <v>163</v>
+      </c>
+      <c r="AC4" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="T4" s="23" t="s">
+      <c r="AD4" s="86" t="s">
+        <v>164</v>
+      </c>
+      <c r="AE4" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="U4" s="23" t="s">
+      <c r="AF4" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="V4" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="W4" s="23" t="s">
+      <c r="AG4" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="X4" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y4" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z4" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="AA4" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB4" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC4" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="AD4" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="AE4" s="26" t="s">
-        <v>163</v>
-      </c>
-      <c r="AF4" s="26" t="s">
-        <v>164</v>
-      </c>
-      <c r="AG4" s="26" t="s">
-        <v>165</v>
-      </c>
       <c r="AH4" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="AI4" s="120"/>
-      <c r="AJ4" s="121"/>
-      <c r="AK4" s="121"/>
-      <c r="AL4" s="121"/>
-      <c r="AM4" s="121"/>
-      <c r="AN4" s="121"/>
-      <c r="AO4" s="121"/>
-      <c r="AP4" s="121"/>
-      <c r="AQ4" s="116"/>
-      <c r="AR4" s="116"/>
-      <c r="AS4" s="121"/>
+        <v>139</v>
+      </c>
+      <c r="AI4" s="124"/>
+      <c r="AJ4" s="125"/>
+      <c r="AK4" s="125"/>
+      <c r="AL4" s="125"/>
+      <c r="AM4" s="125"/>
+      <c r="AN4" s="125"/>
+      <c r="AO4" s="125"/>
+      <c r="AP4" s="125"/>
+      <c r="AQ4" s="120"/>
+      <c r="AR4" s="120"/>
+      <c r="AS4" s="125"/>
     </row>
     <row r="5" spans="1:45" s="2" customFormat="1" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="10"/>
@@ -3827,10 +3891,10 @@
       <c r="I5" s="17"/>
       <c r="J5" s="12"/>
       <c r="K5" s="12" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="M5" s="19"/>
       <c r="N5" s="12"/>
@@ -3849,13 +3913,13 @@
       <c r="AA5" s="25"/>
       <c r="AB5" s="27"/>
       <c r="AC5" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AD5" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AE5" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AF5" s="28"/>
       <c r="AG5" s="28"/>
@@ -3962,7 +4026,7 @@
     <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="J8" s="3"/>
       <c r="L8" s="21" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:45" x14ac:dyDescent="0.25">
@@ -3978,7 +4042,7 @@
       <c r="F14" s="14"/>
       <c r="G14" s="14"/>
       <c r="H14" s="14" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
@@ -4011,15 +4075,15 @@
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="E3:E4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="G3:G4"/>
     <mergeCell ref="H3:H4"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
